--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Redundancia/redundancia_variables.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Redundancia/redundancia_variables.xlsx
@@ -499,11 +499,11 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -547,11 +547,11 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -760,14 +760,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -784,14 +784,14 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -832,14 +832,14 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -856,14 +856,14 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -880,14 +880,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -928,14 +928,14 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -952,14 +952,14 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1000,14 +1000,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.167</v>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1072,14 +1072,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1096,14 +1096,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1147,11 +1147,11 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
